--- a/data/trans_orig/IP2001-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP2001-Estudios-trans_orig.xlsx
@@ -733,7 +733,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8054</t>
+          <t>8237</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7771</t>
+          <t>8005</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18765</t>
+          <t>18385</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18504</t>
+          <t>19342</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34250</t>
+          <t>34399</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,52%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>78889</t>
+          <t>78706</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>61901</t>
+          <t>62281</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>72895</t>
+          <t>72661</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>133359</t>
+          <t>133210</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>149105</t>
+          <t>148267</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>88,46%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26868</t>
+          <t>25823</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45911</t>
+          <t>45256</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24045</t>
+          <t>23543</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41521</t>
+          <t>41079</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>54085</t>
+          <t>54628</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>79419</t>
+          <t>78963</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>347688</t>
+          <t>348343</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>366731</t>
+          <t>367776</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>408617</t>
+          <t>409059</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>426093</t>
+          <t>426595</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>764318</t>
+          <t>764774</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>789652</t>
+          <t>789109</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,53%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2673</t>
+          <t>2901</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11021</t>
+          <t>10715</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5847</t>
+          <t>5857</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16866</t>
+          <t>16646</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10060</t>
+          <t>10417</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23273</t>
+          <t>23467</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,64%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>150286</t>
+          <t>150592</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>158634</t>
+          <t>158406</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>129136</t>
+          <t>129356</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>140155</t>
+          <t>140145</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>284035</t>
+          <t>283841</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>297248</t>
+          <t>296891</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,61%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43146</t>
+          <t>43502</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66270</t>
+          <t>66367</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42973</t>
+          <t>44185</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65718</t>
+          <t>67528</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>93237</t>
+          <t>94570</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>125975</t>
+          <t>124900</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>575579</t>
+          <t>575482</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>598703</t>
+          <t>598347</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>611087</t>
+          <t>609277</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>633832</t>
+          <t>632620</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1192679</t>
+          <t>1193754</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1225417</t>
+          <t>1224084</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,83%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6140</t>
+          <t>6421</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16574</t>
+          <t>15900</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8922</t>
+          <t>8858</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20578</t>
+          <t>21384</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17535</t>
+          <t>17600</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32231</t>
+          <t>32680</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,15%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>71438</t>
+          <t>72112</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>81872</t>
+          <t>81591</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>62047</t>
+          <t>61241</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>73703</t>
+          <t>73767</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>74,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>138406</t>
+          <t>137957</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>153102</t>
+          <t>153037</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,69%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35342</t>
+          <t>35415</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55678</t>
+          <t>56397</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35186</t>
+          <t>34882</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57187</t>
+          <t>57236</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>75132</t>
+          <t>75170</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>106323</t>
+          <t>106707</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,15%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>360438</t>
+          <t>359719</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>380774</t>
+          <t>380701</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>405130</t>
+          <t>405081</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>427131</t>
+          <t>427435</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>772110</t>
+          <t>771726</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>803301</t>
+          <t>803263</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,44%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2736</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10937</t>
+          <t>10975</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3173</t>
+          <t>3462</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12717</t>
+          <t>12651</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8296</t>
+          <t>8364</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20588</t>
+          <t>19969</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,43%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>144156</t>
+          <t>144118</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>152357</t>
+          <t>152339</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>142564</t>
+          <t>142630</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>152108</t>
+          <t>151819</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>289786</t>
+          <t>290405</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>302078</t>
+          <t>302010</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,31%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51020</t>
+          <t>49264</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>77399</t>
+          <t>74585</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>54034</t>
+          <t>52945</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>80453</t>
+          <t>80410</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>110064</t>
+          <t>110265</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>149192</t>
+          <t>147580</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,86%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>581822</t>
+          <t>584636</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>608201</t>
+          <t>609957</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>619770</t>
+          <t>619813</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>646189</t>
+          <t>647278</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1210252</t>
+          <t>1211864</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1249380</t>
+          <t>1249179</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,89%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16415</t>
+          <t>15673</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5590</t>
+          <t>6122</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15636</t>
+          <t>15236</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14383</t>
+          <t>14545</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28429</t>
+          <t>27570</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,2%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40399</t>
+          <t>41141</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50617</t>
+          <t>50591</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51738</t>
+          <t>52138</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>61784</t>
+          <t>61252</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>95759</t>
+          <t>96618</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>109805</t>
+          <t>109643</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>77,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,29%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39333</t>
+          <t>38021</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61793</t>
+          <t>59606</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36312</t>
+          <t>35696</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57846</t>
+          <t>56965</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>80221</t>
+          <t>80141</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>110882</t>
+          <t>110552</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,25%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>377542</t>
+          <t>379729</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>400002</t>
+          <t>401314</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>405293</t>
+          <t>406174</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>426827</t>
+          <t>427443</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>791592</t>
+          <t>791922</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>822253</t>
+          <t>822333</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,12%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5688</t>
+          <t>6001</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15543</t>
+          <t>16376</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7313</t>
+          <t>7515</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18961</t>
+          <t>18514</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15665</t>
+          <t>15194</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30705</t>
+          <t>30363</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,15%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>147160</t>
+          <t>146327</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>157015</t>
+          <t>156702</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>150131</t>
+          <t>150578</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>161779</t>
+          <t>161577</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>301091</t>
+          <t>301433</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>316131</t>
+          <t>316602</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,42%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>57365</t>
+          <t>57351</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>83173</t>
+          <t>81317</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55615</t>
+          <t>55501</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>82868</t>
+          <t>82084</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>120256</t>
+          <t>119580</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>155821</t>
+          <t>153733</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>575679</t>
+          <t>577535</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>601487</t>
+          <t>601501</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>616737</t>
+          <t>617521</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>643990</t>
+          <t>644104</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1202636</t>
+          <t>1204724</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1238201</t>
+          <t>1238877</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,2%</t>
         </is>
       </c>
     </row>
@@ -5577,47 +5577,47 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>934</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>8412</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>4,94%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>14,07%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>2956</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>929</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>8082</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>4,94%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>13,51%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2956</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>909</t>
-        </is>
-      </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8427</t>
+          <t>7969</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,02%</t>
         </is>
       </c>
     </row>
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51721</t>
+          <t>51391</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58874</t>
+          <t>58869</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>105075</t>
+          <t>105533</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>112593</t>
+          <t>112573</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,18%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13972</t>
+          <t>14205</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29888</t>
+          <t>29520</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19151</t>
+          <t>20220</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39627</t>
+          <t>40240</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38429</t>
+          <t>38074</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>64449</t>
+          <t>64260</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>422276</t>
+          <t>422644</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>438192</t>
+          <t>437959</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>464475</t>
+          <t>463862</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>484951</t>
+          <t>483882</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>891816</t>
+          <t>892005</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>917836</t>
+          <t>918191</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,02%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3822</t>
+          <t>3699</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12444</t>
+          <t>12119</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8338</t>
+          <t>8430</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22832</t>
+          <t>23038</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13589</t>
+          <t>14151</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30594</t>
+          <t>30733</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,34%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>134672</t>
+          <t>134997</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>143294</t>
+          <t>143417</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>159247</t>
+          <t>159041</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>173741</t>
+          <t>173649</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>298602</t>
+          <t>298463</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>315607</t>
+          <t>315045</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,7%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20572</t>
+          <t>20503</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38658</t>
+          <t>38040</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33339</t>
+          <t>32717</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57334</t>
+          <t>57977</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>58316</t>
+          <t>58732</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>88997</t>
+          <t>89839</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,42%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>614321</t>
+          <t>614939</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>632407</t>
+          <t>632476</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>688650</t>
+          <t>688007</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>712645</t>
+          <t>713267</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1309966</t>
+          <t>1309124</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1340647</t>
+          <t>1340231</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,8%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP2001-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP2001-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>12769</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7956</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>18779</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>15,83%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>9,86%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>23,28%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>13138</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>8237</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>18975</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>8430</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>19787</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>15,11%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9,47%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>21,82%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>12769</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>8005</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>18385</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>15,83%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19342</t>
+          <t>19170</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34399</t>
+          <t>33626</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,06%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>67897</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>61887</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>72710</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>84,17%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>76,72%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>90,14%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>73805</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>67968</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>78706</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>67156</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>78513</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>84,89%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>78,18%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>90,53%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>67897</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>62281</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>72661</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>84,17%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>133210</t>
+          <t>133983</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>148267</t>
+          <t>148439</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,56%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>80666</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>80666</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>80666</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>130</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>86943</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>86943</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>86943</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>80666</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>80666</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>80666</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>31376</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>23563</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>40466</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6,97%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5,23%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,99%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>35169</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>25823</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>45256</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>26754</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>45727</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>8,94%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6,56%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>11,5%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>31376</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>23543</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>41079</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>6,97%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>54628</t>
+          <t>54940</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>78963</t>
+          <t>79363</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,41%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>631</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>418762</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>409672</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>426575</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>93,03%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>91,01%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>94,77%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>541</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>358430</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>348343</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>367776</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>347872</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>366845</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>91,06%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>88,5%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>93,44%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>631</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>418762</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>409059</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>426595</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>93,03%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>764774</t>
+          <t>764374</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>789109</t>
+          <t>788797</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,49%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>450138</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>450138</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>450138</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>593</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>393599</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>393599</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>393599</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>679</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>450138</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>450138</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>450138</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9942</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5646</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>15749</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>6,81%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,87%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>10,79%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>5870</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2901</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>10715</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2810</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>10762</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>3,64%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,64%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>9942</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>5857</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>16646</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10417</t>
+          <t>9846</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23467</t>
+          <t>23381</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>136060</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>130253</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>140356</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>93,19%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>89,21%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>96,13%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>155437</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>150592</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>158406</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>150545</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>158497</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>96,36%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>93,36%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,2%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>136060</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>129356</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>140145</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>93,19%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>283841</t>
+          <t>283927</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>296891</t>
+          <t>297462</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,8%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>146002</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>146002</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>146002</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>161307</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>161307</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>161307</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>146002</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>146002</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>146002</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1757,67 +1757,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>54087</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>43065</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>65260</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>7,99%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>6,36%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>9,64%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>54177</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>43502</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>66367</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>43339</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>66323</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>8,44%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6,78%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>10,34%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>54087</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>44185</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>67528</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>7,99%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>94570</t>
+          <t>93217</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>124900</t>
+          <t>124482</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>937</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>622718</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>611545</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>633740</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>92,01%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>90,36%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>93,64%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>877</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>587672</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>575482</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>598347</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>575526</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>598510</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>91,56%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>89,66%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>93,22%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>937</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>622718</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>609277</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>632620</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>92,01%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1193754</t>
+          <t>1194172</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1224084</t>
+          <t>1225437</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,93%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1018</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>676805</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>676805</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>676805</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>958</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>641849</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>641849</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>641849</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1018</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>676805</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>676805</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>676805</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,72 +2326,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>13968</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9163</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>20661</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>16,9%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>11,09%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>25,01%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>10379</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6421</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>15900</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>6412</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>15960</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>11,79%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7,3%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>18,07%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>13968</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>8858</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>21384</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>16,9%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17600</t>
+          <t>16421</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32680</t>
+          <t>32295</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>18,93%</t>
         </is>
       </c>
     </row>
@@ -2439,72 +2439,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>68657</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>61964</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>73462</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>83,1%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>74,99%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>88,91%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>77633</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>72112</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>81591</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>72052</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>81600</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>88,21%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>81,93%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>92,7%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>68657</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>61241</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>73767</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>83,1%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>137957</t>
+          <t>138342</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>153037</t>
+          <t>154216</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>90,38%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>82625</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>82625</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>82625</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>88012</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>88012</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>88012</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>82625</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>82625</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>82625</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2674,67 +2674,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>44884</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>34006</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>56951</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>9,71%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>7,36%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>12,32%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>45040</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>35415</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>56397</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>35904</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>57583</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>10,82%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>8,51%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>13,55%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>44884</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>34882</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>57236</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>9,71%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>75170</t>
+          <t>77038</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>106707</t>
+          <t>106595</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,13%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>417433</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>405366</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>428311</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>90,29%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>87,68%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>92,64%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>539</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>371076</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>359719</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>380701</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>358533</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>380212</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>89,18%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>86,45%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>91,49%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>601</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>417433</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>405081</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>427435</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>90,29%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>771726</t>
+          <t>771838</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>803263</t>
+          <t>801395</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,23%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>664</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>462317</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>462317</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>462317</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>602</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>416116</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>416116</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>416116</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>664</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>462317</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>462317</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>462317</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3017,67 +3017,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>7106</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3396</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>13442</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4,58%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>8,66%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>6076</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2754</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>10975</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2684</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>10808</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>3,92%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,78%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,08%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>7106</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>3462</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>12651</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>4,58%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8364</t>
+          <t>8081</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19969</t>
+          <t>20312</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>148175</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>141839</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>151885</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>95,42%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>91,34%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,81%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>210</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>149017</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>144118</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>152339</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>144285</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>152409</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>96,08%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>92,92%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,22%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>148175</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>142630</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>151819</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>95,42%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>290405</t>
+          <t>290062</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>302010</t>
+          <t>302293</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,4%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>155281</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>155281</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>155281</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>155093</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>155093</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>155093</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>155281</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>155281</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>155281</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>65958</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>55249</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>80516</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>9,42%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>7,89%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>11,5%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>61495</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>49264</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>74585</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>48968</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>72618</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>9,33%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7,47%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>11,31%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>65958</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>52945</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>80410</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>9,42%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>110265</t>
+          <t>110562</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>147580</t>
+          <t>146583</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,78%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>909</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>634265</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>619707</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>644974</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>90,58%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>88,5%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>92,11%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>861</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>597726</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>584636</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>609957</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>586603</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>610253</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>90,67%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>88,69%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>92,53%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>909</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>634265</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>619813</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>647278</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>90,58%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1211864</t>
+          <t>1212861</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1249179</t>
+          <t>1248882</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,87%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>700223</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>700223</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>700223</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>949</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>659221</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>659221</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>659221</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>700223</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>700223</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>700223</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3934,67 +3934,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>9846</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5866</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>15331</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>14,61%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>8,71%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>22,76%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>10425</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6223</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>15673</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>6203</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>16337</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>18,35%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>10,95%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>27,59%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>9846</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>6122</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>15236</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>14,61%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14545</t>
+          <t>14493</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27570</t>
+          <t>28138</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,66%</t>
         </is>
       </c>
     </row>
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>57528</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>52043</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>61508</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>85,39%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>77,24%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>91,29%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>46389</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>41141</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>50591</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>40477</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>50611</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>81,65%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>72,41%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>89,05%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>57528</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>52138</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>61252</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>85,39%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>96618</t>
+          <t>96050</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>109643</t>
+          <t>109695</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,33%</t>
         </is>
       </c>
     </row>
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>67374</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>67374</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>67374</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>56814</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>56814</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>56814</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>67374</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>67374</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>67374</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>45757</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>35959</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>57728</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>9,88%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>7,76%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>12,46%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>48860</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>38021</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>59606</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>38969</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>59794</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>11,12%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>8,65%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>13,57%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>45757</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>35696</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>56965</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>9,88%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>80141</t>
+          <t>79035</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>110552</t>
+          <t>109511</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,13%</t>
         </is>
       </c>
     </row>
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>595</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>417382</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>405411</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>427180</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>90,12%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>87,54%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>92,24%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>586</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>390475</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>379729</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>401314</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>379541</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>400366</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>88,88%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>86,43%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>91,35%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>595</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>417382</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>406174</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>427443</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>90,12%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>791922</t>
+          <t>792963</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>822333</t>
+          <t>823439</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>91,24%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>658</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>463139</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>463139</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>463139</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>661</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>439335</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>439335</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>439335</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>658</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>463139</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>463139</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>463139</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,72 +4615,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>12351</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7727</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>19313</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7,3%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4,57%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>11,42%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>9897</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>6001</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>16376</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>5598</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>16532</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>6,08%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,69%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>10,06%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>12351</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>7515</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>18514</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>7,3%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15194</t>
+          <t>14840</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30363</t>
+          <t>30608</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,22%</t>
         </is>
       </c>
     </row>
@@ -4728,72 +4728,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>156741</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>149779</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>161365</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>92,7%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>88,58%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>95,43%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>152806</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>146327</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>156702</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>146171</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>157105</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>93,92%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>89,94%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>96,31%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>156741</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>150578</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>161577</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>92,7%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>301433</t>
+          <t>301188</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>316602</t>
+          <t>316956</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,53%</t>
         </is>
       </c>
     </row>
@@ -4846,52 +4846,52 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>169092</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>169092</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>169092</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
           <t>162703</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>162703</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>162703</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>169092</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>169092</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>169092</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,72 +4958,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>67954</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>55272</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>81936</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>9,71%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>7,9%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>11,71%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>69182</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>57351</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>81317</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>56179</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>82855</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>10,5%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>8,7%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>12,34%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>67954</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>55501</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>82084</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>9,71%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>119580</t>
+          <t>119570</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>153733</t>
+          <t>157149</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>903</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>631651</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>617669</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>644333</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>90,29%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>88,29%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>92,1%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>885</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>589670</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>577535</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>601501</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>575997</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>602673</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>89,5%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>87,66%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>91,3%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>903</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>631651</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>617521</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>644104</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>90,29%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1204724</t>
+          <t>1201308</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1238877</t>
+          <t>1238887</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>998</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>699605</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>699605</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>699605</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>989</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>658852</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>658852</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>658852</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>998</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>699605</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>699605</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>699605</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,107 +5532,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2924</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7459</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5,32%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>13,58%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2956</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>934</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>8412</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>4,94%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>14,07%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2956</t>
+          <t>2924</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>931</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7969</t>
+          <t>7980</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,91%</t>
         </is>
       </c>
     </row>
@@ -5645,74 +5645,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>52009</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>47474</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>54026</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>94,68%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>86,42%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,35%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>45905</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>56847</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>51391</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>58869</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>95,06%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>85,93%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>98,44%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>144</t>
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>110546</t>
+          <t>97914</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>105533</t>
+          <t>92858</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>112573</t>
+          <t>99907</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>54933</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>54933</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>54933</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>59803</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>59803</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>59803</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>113502</t>
+          <t>100838</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>113502</t>
+          <t>100838</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>113502</t>
+          <t>100838</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>26370</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>18075</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>37115</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5,67%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,88%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7,98%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>21267</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>14205</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>29520</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>4,7%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,14%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6,53%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>28021</t>
+          <t>21567</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20220</t>
+          <t>14929</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40240</t>
+          <t>30028</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>49288</t>
+          <t>47937</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38074</t>
+          <t>37718</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>64260</t>
+          <t>59543</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,69%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>595</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>438995</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>428250</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>447290</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>94,33%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>92,02%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,12%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>594</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>430897</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>422644</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>437959</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>95,3%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>93,47%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,86%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>595</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>476081</t>
+          <t>403515</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>463862</t>
+          <t>395054</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>483882</t>
+          <t>410153</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>906977</t>
+          <t>842510</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>892005</t>
+          <t>830904</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>918191</t>
+          <t>852729</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,76%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>465365</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>465365</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>465365</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>626</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>452164</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>452164</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>452164</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>630</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>504102</t>
+          <t>425082</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>504102</t>
+          <t>425082</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>504102</t>
+          <t>425082</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>956265</t>
+          <t>890447</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>956265</t>
+          <t>890447</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>956265</t>
+          <t>890447</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,72 +6218,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13208</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7581</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>21242</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7,89%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4,53%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>12,69%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>7187</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3699</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>12119</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4,89%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,51%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8,24%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>13781</t>
+          <t>6958</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8430</t>
+          <t>3896</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23038</t>
+          <t>12783</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,27 +6293,27 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>20968</t>
+          <t>20166</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14151</t>
+          <t>13767</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30733</t>
+          <t>29460</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -6331,72 +6331,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>154188</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>146154</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>159815</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>92,11%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>87,31%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>95,47%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>212</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>139929</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>134997</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>143417</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>95,11%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>91,76%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,49%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>168298</t>
+          <t>140975</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>159041</t>
+          <t>135150</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>173649</t>
+          <t>144037</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,22 +6406,22 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>308228</t>
+          <t>295164</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>298463</t>
+          <t>285870</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>315045</t>
+          <t>301563</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,63%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>167396</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>167396</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>167396</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>224</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>147116</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>147116</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>147116</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>182079</t>
+          <t>147933</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>182079</t>
+          <t>147933</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>182079</t>
+          <t>147933</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>329196</t>
+          <t>315330</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>329196</t>
+          <t>315330</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>329196</t>
+          <t>315330</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>42502</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>31994</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>56115</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6,18%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4,65%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8,16%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>28454</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>20503</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>38040</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>4,36%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,14%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,83%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>44758</t>
+          <t>28525</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32717</t>
+          <t>20833</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57977</t>
+          <t>38301</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>73212</t>
+          <t>71027</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>58732</t>
+          <t>59455</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>89839</t>
+          <t>87653</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>645193</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>631580</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>655701</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>93,82%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>91,84%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>95,35%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>873</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>624525</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>614939</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>632476</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>95,64%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>94,17%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>96,86%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>891</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>701226</t>
+          <t>590394</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>688007</t>
+          <t>580618</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>713267</t>
+          <t>598086</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1325751</t>
+          <t>1235588</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1309124</t>
+          <t>1218962</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1340231</t>
+          <t>1247160</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,45%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>687695</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>687695</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>687695</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>917</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>652979</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>652979</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>652979</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>745984</t>
+          <t>618919</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>745984</t>
+          <t>618919</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>745984</t>
+          <t>618919</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1398963</t>
+          <t>1306615</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1398963</t>
+          <t>1306615</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1398963</t>
+          <t>1306615</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
